--- a/backtest_runs/20260410_193731/by_symbol/NONS/NONS.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/NONS/NONS.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>100000</v>
@@ -863,7 +863,7 @@
         <v>-2584.190000000001</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>97415.81</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>97415.81</v>
@@ -1139,7 +1139,7 @@
         <v>-674.6900000000014</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>97428.54000000001</v>
@@ -1185,7 +1185,7 @@
         <v>-2418.700000000007</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>95009.84</v>
@@ -1277,7 +1277,7 @@
         <v>-776.5299999999993</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>94233.31</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>94233.31</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>98994.32999999999</v>
@@ -1461,7 +1461,7 @@
         <v>-471.0100000000058</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>98523.31999999999</v>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>104888.32</v>
